--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1160,523 +1160,808 @@
   </cols>
   <sheetData>
     <row r="1" s="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>resName</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>power</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>bulletId</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>targetMode</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>searchIntervalMs</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>rotateSpeed</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>upgradeTo</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>sellPrice</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>effectValue</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2" s="1">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">string </t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">int </t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">int </t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3" s="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>资源名（对应 ResTable 逻辑名）</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>攻击半径</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>攻击力</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>攻击间隔</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>价格(这是增量)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>发射的子弹 id → TBBulletData</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>索敌策略 0路径最靠前/1最近/2最高血</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>索敌间隔（毫秒，节流用）</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>炮管转向速度（度/秒）</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>下一等级 id，0=满级</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>出售返还金币（累计成本 70%）</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="0" t="inlineStr">
         <is>
           <t>特殊效果类型 0无/1减速/2持续伤害</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="0" t="inlineStr">
         <is>
           <t>特殊效果参数</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4" s="1">
-      <c r="B4" t="n">
+      <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>NormalTower</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>NormalTower</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>NormalTower</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
       <c r="A7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="8" t="n"/>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PowerTower</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tower_Power</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" t="n">
+        <v>360</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="2">
       <c r="A8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="8" t="n"/>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PowerTower</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Tower_Power</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>360</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="2">
       <c r="A9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PowerTower</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Tower_Power</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" t="n">
+        <v>360</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="2">
       <c r="A10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="11" t="n"/>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RetardTower</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Tower_Retard</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N10" t="n">
+        <v>360</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="2">
       <c r="A11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="3" t="n"/>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RetardTower</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Tower_Retard</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>360</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="12" s="1">
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RetardTower</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tower_Retard</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>300</v>
+      </c>
+      <c r="J12" t="n">
+        <v>70</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>360</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="13" s="1">
       <c r="L13" s="12" t="n"/>

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -1255,6 +1255,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>canAttackAir</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="1">
       <c r="A2" s="0" t="inlineStr">
@@ -1352,6 +1357,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="1">
       <c r="A3" s="0" t="inlineStr">
@@ -1431,7 +1441,7 @@
       </c>
       <c r="Q3" s="0" t="inlineStr">
         <is>
-          <t>特殊效果类型 0无/1减速/2持续伤害</t>
+          <t>特殊效果类型 0无/1减速/2持续伤害/3范围伤害/4激光</t>
         </is>
       </c>
       <c r="R3" s="0" t="inlineStr">
@@ -1442,6 +1452,11 @@
       <c r="S3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>是否可攻击飞行单位 0否/1是（缺省视为 1，兼容旧表）</t>
         </is>
       </c>
     </row>
@@ -1500,6 +1515,9 @@
       </c>
       <c r="R4" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1558,6 +1576,9 @@
       <c r="R5" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="n">
@@ -1615,16 +1636,19 @@
       <c r="R6" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="2">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>PowerTower</t>
         </is>
@@ -1650,39 +1674,42 @@
         <v>35</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
+      <c r="Q7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="1" s="2">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" t="n">
+      <c r="B8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>PowerTower</t>
         </is>
@@ -1708,7 +1735,7 @@
         <v>55</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0</v>
@@ -1716,31 +1743,34 @@
       <c r="M8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
+      <c r="Q8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="1" s="2">
       <c r="A9" s="4" t="n"/>
-      <c r="B9" t="n">
+      <c r="B9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>PowerTower</t>
         </is>
@@ -1766,39 +1796,42 @@
         <v>85</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="O9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="0" t="n">
         <v>122</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
+      <c r="Q9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="1" s="2">
       <c r="A10" s="4" t="n"/>
-      <c r="B10" t="n">
+      <c r="B10" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>RetardTower</t>
         </is>
@@ -1824,7 +1857,7 @@
         <v>30</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>0</v>
@@ -1832,31 +1865,34 @@
       <c r="M10" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="Q10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="0" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="1" s="2">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>RetardTower</t>
         </is>
@@ -1882,7 +1918,7 @@
         <v>45</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>0</v>
@@ -1890,56 +1926,59 @@
       <c r="M11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="Q11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="0" t="n">
         <v>0.6</v>
       </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" s="1">
-      <c r="B12" t="n">
+      <c r="B12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>RetardTower</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Tower_Retard</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="K12" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>0</v>
@@ -1947,20 +1986,23 @@
       <c r="M12" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="O12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="0" t="n">
         <v>102</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="Q12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="0" t="n">
         <v>0.7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13" s="1">
@@ -1998,8 +2040,394 @@
       <c r="M20" s="12" t="n"/>
     </row>
     <row r="21" s="1">
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PierceTower</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>200</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" t="n">
+        <v>360</v>
+      </c>
+      <c r="O21" t="n">
+        <v>11</v>
+      </c>
+      <c r="P21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>穿透塔 L1：低伤高频，子弹可连续穿透多个敌人</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PierceTower</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>170</v>
+      </c>
+      <c r="J22" t="n">
+        <v>45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" t="n">
+        <v>360</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>穿透塔 L2</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PierceTower</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" t="n">
+        <v>140</v>
+      </c>
+      <c r="J23" t="n">
+        <v>65</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100</v>
+      </c>
+      <c r="N23" t="n">
+        <v>360</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>穿透塔 L3</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LaserTower</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I24" t="n">
+        <v>500</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" t="n">
+        <v>360</v>
+      </c>
+      <c r="O24" t="n">
+        <v>14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>激光塔 L1：瞬发命中（hitscan），不发射弹体；bulletId=0 表示无子弹</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LaserTower</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>18</v>
+      </c>
+      <c r="I25" t="n">
+        <v>450</v>
+      </c>
+      <c r="J25" t="n">
+        <v>60</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" t="n">
+        <v>360</v>
+      </c>
+      <c r="O25" t="n">
+        <v>15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>激光塔 L2</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LaserTower</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24</v>
+      </c>
+      <c r="I26" t="n">
+        <v>400</v>
+      </c>
+      <c r="J26" t="n">
+        <v>80</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" t="n">
+        <v>360</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>激光塔 L3</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1255,7 +1255,7 @@
           <t>desc</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>canAttackAir</t>
         </is>
@@ -1357,7 +1357,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1454,7 +1454,7 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="0" t="inlineStr">
         <is>
           <t>是否可攻击飞行单位 0否/1是（缺省视为 1，兼容旧表）</t>
         </is>
@@ -1516,7 +1516,7 @@
       <c r="R4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>200</v>
@@ -1576,7 +1576,7 @@
       <c r="R5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       <c r="R6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       <c r="R7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>500</v>
@@ -1758,7 +1758,7 @@
       <c r="R8" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>400</v>
@@ -1819,7 +1819,7 @@
       <c r="R9" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>400</v>
@@ -1880,7 +1880,7 @@
       <c r="R10" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>350</v>
@@ -1941,7 +1941,7 @@
       <c r="R11" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>6</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>300</v>
@@ -2001,7 +2001,7 @@
       <c r="R12" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2040,38 +2040,38 @@
       <c r="M20" s="12" t="n"/>
     </row>
     <row r="21" s="1">
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>PierceTower</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="0" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="12" t="n">
@@ -2080,352 +2080,352 @@
       <c r="M21" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="Q21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="0" t="inlineStr">
         <is>
           <t>穿透塔 L1：低伤高频，子弹可连续穿透多个敌人</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="U21" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>PierceTower</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="H22" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H22" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="Q22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="0" t="inlineStr">
         <is>
           <t>穿透塔 L2</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="U22" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>PierceTower</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H23" t="n">
-        <v>11</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H23" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I23" s="0" t="n">
         <v>140</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="O23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="0" t="n">
         <v>98</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="Q23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="0" t="inlineStr">
         <is>
           <t>穿透塔 L3</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="U23" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>LaserTower</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="O24" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I24" t="n">
-        <v>500</v>
-      </c>
-      <c r="J24" t="n">
-        <v>40</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="P24" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="0" t="inlineStr">
+        <is>
+          <t>激光塔 L1：瞬发命中（hitscan），不发射弹体；bulletId=0 表示无子弹</t>
+        </is>
+      </c>
+      <c r="U24" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>LaserTower</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>Tower_Normal</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>450</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O24" t="n">
-        <v>14</v>
-      </c>
-      <c r="P24" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="O25" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="P25" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q25" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>激光塔 L1：瞬发命中（hitscan），不发射弹体；bulletId=0 表示无子弹</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="R25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="0" t="inlineStr">
+        <is>
+          <t>激光塔 L2</t>
+        </is>
+      </c>
+      <c r="U25" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>LaserTower</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Tower_Normal</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>18</v>
-      </c>
-      <c r="I25" t="n">
-        <v>450</v>
-      </c>
-      <c r="J25" t="n">
-        <v>60</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="F26" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="O25" t="n">
-        <v>15</v>
-      </c>
-      <c r="P25" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="O26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="0" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q26" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>激光塔 L2</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="n">
-        <v>15</v>
-      </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LaserTower</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Tower_Normal</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>24</v>
-      </c>
-      <c r="I26" t="n">
-        <v>400</v>
-      </c>
-      <c r="J26" t="n">
-        <v>80</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>100</v>
-      </c>
-      <c r="N26" t="n">
-        <v>360</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="R26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="0" t="inlineStr">
         <is>
           <t>激光塔 L3</t>
         </is>
       </c>
-      <c r="U26" t="n">
+      <c r="U26" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Tower_Power</t>
+          <t>Tower_Power0</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Tower_Power</t>
+          <t>Tower_Power1</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Tower_Power</t>
+          <t>Tower_Power2</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Tower_Retard</t>
+          <t>Tower_Retard0</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Tower_Retard</t>
+          <t>Tower_Retard1</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>Tower_Retard</t>
+          <t>Tower_Retard2</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1396,12 +1396,12 @@
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>攻击力</t>
+          <t>攻击力（减速塔=光环，本列不参与运行）</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>攻击间隔</t>
+          <t>攻击间隔（减速塔=光环施加节拍）</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>发射的子弹 id → TBBulletData</t>
+          <t>发射的子弹 id → TBBulletData（减速塔填 0，不发射）</t>
         </is>
       </c>
       <c r="L3" s="0" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="Q3" s="0" t="inlineStr">
         <is>
-          <t>特殊效果类型 0无/1减速/2持续伤害/3范围伤害/4激光</t>
+          <t>特殊效果类型 0无/1减速(光环)/2持续伤害/3范围伤害/4激光</t>
         </is>
       </c>
       <c r="R3" s="0" t="inlineStr">
         <is>
-          <t>特殊效果参数</t>
+          <t>特殊效果参数（减速=减速比例 0~1）</t>
         </is>
       </c>
       <c r="S3" s="0" t="inlineStr">
@@ -1857,7 +1857,7 @@
         <v>30</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>45</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>70</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>0</v>

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal1</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal2</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F21" s="0" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F22" s="0" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F23" s="0" t="n">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F25" s="0" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>Tower_Normal</t>
+          <t>Tower_Normal0</t>
         </is>
       </c>
       <c r="F26" s="0" t="n">

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>类型 1普通/2火力(AOE)/3减速光环</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Q3" s="0" t="inlineStr">
         <is>
-          <t>特殊效果类型 0无/1减速(光环)/2持续伤害/3范围伤害/4激光</t>
+          <t>特殊效果类型 0无/1减速(光环)/2持续伤害/3范围伤害</t>
         </is>
       </c>
       <c r="R3" s="0" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>是否可攻击飞行单位 0否/1是（缺省视为 1，兼容旧表）</t>
+          <t>是否可攻击飞行单位 0否/1是（留空视为 0。三塔型定案：普通1/火力0/减速1）</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="1" s="2">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="1" s="2">
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="1" s="2">
@@ -2039,396 +2039,7 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="12" t="n"/>
     </row>
-    <row r="21" s="1">
-      <c r="B21" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>PierceTower</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>Tower_Normal0</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="N21" s="0" t="n">
-        <v>360</v>
-      </c>
-      <c r="O21" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="P21" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="0" t="inlineStr">
-        <is>
-          <t>穿透塔 L1：低伤高频，子弹可连续穿透多个敌人</t>
-        </is>
-      </c>
-      <c r="U21" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>PierceTower</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>Tower_Normal0</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" s="0" t="n">
-        <v>170</v>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>45</v>
-      </c>
-      <c r="K22" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="N22" s="0" t="n">
-        <v>360</v>
-      </c>
-      <c r="O22" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="P22" s="0" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="0" t="inlineStr">
-        <is>
-          <t>穿透塔 L2</t>
-        </is>
-      </c>
-      <c r="U22" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="C23" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>PierceTower</t>
-        </is>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>Tower_Normal0</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="I23" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="J23" s="0" t="n">
-        <v>65</v>
-      </c>
-      <c r="K23" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="N23" s="0" t="n">
-        <v>360</v>
-      </c>
-      <c r="O23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="0" t="inlineStr">
-        <is>
-          <t>穿透塔 L3</t>
-        </is>
-      </c>
-      <c r="U23" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>LaserTower</t>
-        </is>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>Tower_Normal0</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="I24" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="J24" s="0" t="n">
-        <v>40</v>
-      </c>
-      <c r="K24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="N24" s="0" t="n">
-        <v>360</v>
-      </c>
-      <c r="O24" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="P24" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q24" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="R24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="0" t="inlineStr">
-        <is>
-          <t>激光塔 L1：瞬发命中（hitscan），不发射弹体；bulletId=0 表示无子弹</t>
-        </is>
-      </c>
-      <c r="U24" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>LaserTower</t>
-        </is>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>Tower_Normal0</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="I25" s="0" t="n">
-        <v>450</v>
-      </c>
-      <c r="J25" s="0" t="n">
-        <v>60</v>
-      </c>
-      <c r="K25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="N25" s="0" t="n">
-        <v>360</v>
-      </c>
-      <c r="O25" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="P25" s="0" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q25" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="0" t="inlineStr">
-        <is>
-          <t>激光塔 L2</t>
-        </is>
-      </c>
-      <c r="U25" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>LaserTower</t>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t>Tower_Normal0</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H26" s="0" t="n">
-        <v>78</v>
-      </c>
-      <c r="I26" s="0" t="n">
-        <v>400</v>
-      </c>
-      <c r="J26" s="0" t="n">
-        <v>80</v>
-      </c>
-      <c r="K26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="N26" s="0" t="n">
-        <v>360</v>
-      </c>
-      <c r="O26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="0" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q26" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="0" t="inlineStr">
-        <is>
-          <t>激光塔 L3</t>
-        </is>
-      </c>
-      <c r="U26" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="21" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>NormalTower</t>
+          <t>Normal Tower</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>NormalTower</t>
+          <t>Normal Tower</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>NormalTower</t>
+          <t>Normal Tower</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>PowerTower</t>
+          <t>Blast Tower</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>PowerTower</t>
+          <t>Blast Tower</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>PowerTower</t>
+          <t>Blast Tower</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>RetardTower</t>
+          <t>Frost Tower</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>RetardTower</t>
+          <t>Frost Tower</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>RetardTower</t>
+          <t>Frost Tower</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1484,13 +1484,13 @@
         <v>3</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1508,13 +1508,18 @@
         <v>2</v>
       </c>
       <c r="P4" s="0" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="S4" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 25; cumulative 25; continuous theoretical DPS=15</t>
+        </is>
       </c>
       <c r="U4" s="0" t="n">
         <v>1</v>
@@ -1541,16 +1546,16 @@
         <v>2</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="0" t="n">
         <v>14</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1568,13 +1573,18 @@
         <v>3</v>
       </c>
       <c r="P5" s="0" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="S5" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 40; cumulative 65; continuous theoretical DPS=35</t>
+        </is>
       </c>
       <c r="U5" s="0" t="n">
         <v>1</v>
@@ -1601,16 +1611,16 @@
         <v>3</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1628,13 +1638,18 @@
         <v>0</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="S6" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 65; cumulative 130; continuous theoretical DPS=80</t>
+        </is>
       </c>
       <c r="U6" s="0" t="n">
         <v>1</v>
@@ -1665,13 +1680,13 @@
         <v>3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>2</v>
@@ -1689,13 +1704,18 @@
         <v>5</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="Q7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="R7" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="S7" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 45; cumulative 45; continuous theoretical DPS=14</t>
+        </is>
       </c>
       <c r="U7" s="0" t="n">
         <v>0</v>
@@ -1723,16 +1743,16 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>2</v>
@@ -1750,13 +1770,18 @@
         <v>6</v>
       </c>
       <c r="P8" s="0" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="Q8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="R8" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="S8" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 60; cumulative 105; continuous theoretical DPS=31.1111</t>
+        </is>
       </c>
       <c r="U8" s="0" t="n">
         <v>0</v>
@@ -1784,16 +1809,16 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>2</v>
@@ -1811,13 +1836,18 @@
         <v>0</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="Q9" s="0" t="n">
         <v>3</v>
       </c>
       <c r="R9" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="S9" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 100; cumulative 205; continuous theoretical DPS=56.25</t>
+        </is>
       </c>
       <c r="U9" s="0" t="n">
         <v>0</v>
@@ -1845,16 +1875,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>400</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -1872,13 +1902,18 @@
         <v>8</v>
       </c>
       <c r="P10" s="0" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="R10" s="0" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
+      </c>
+      <c r="S10" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 35; cumulative 35; slow aura; DPS=0</t>
+        </is>
       </c>
       <c r="U10" s="0" t="n">
         <v>1</v>
@@ -1906,16 +1941,16 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1933,13 +1968,18 @@
         <v>9</v>
       </c>
       <c r="P11" s="0" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="R11" s="0" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
+      </c>
+      <c r="S11" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 50; cumulative 85; slow aura; DPS=0</t>
+        </is>
       </c>
       <c r="U11" s="0" t="n">
         <v>1</v>
@@ -1966,16 +2006,16 @@
         <v>3</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>0</v>
@@ -1993,13 +2033,18 @@
         <v>0</v>
       </c>
       <c r="P12" s="0" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="Q12" s="0" t="n">
         <v>1</v>
       </c>
       <c r="R12" s="0" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
+      </c>
+      <c r="S12" s="0" t="inlineStr">
+        <is>
+          <t>Incremental cost 80; cumulative 165; slow aura; DPS=0</t>
+        </is>
       </c>
       <c r="U12" s="0" t="n">
         <v>1</v>

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1481,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="0" t="n">
         <v>6</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="J4" s="0" t="n">
         <v>25</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="S4" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 25; cumulative 25; continuous theoretical DPS=15</t>
+          <t>Incremental cost 25; cumulative 25; continuous theoretical DPS=13.3333</t>
         </is>
       </c>
       <c r="U4" s="0" t="n">
@@ -1546,16 +1546,16 @@
         <v>2</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1573,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="P5" s="0" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="0" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="S5" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 40; cumulative 65; continuous theoretical DPS=35</t>
+          <t>Incremental cost 45; cumulative 70; continuous theoretical DPS=22.2222</t>
         </is>
       </c>
       <c r="U5" s="0" t="n">
@@ -1611,16 +1611,16 @@
         <v>3</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="Q6" s="0" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 65; cumulative 130; continuous theoretical DPS=80</t>
+          <t>Incremental cost 75; cumulative 145; continuous theoretical DPS=31.1111</t>
         </is>
       </c>
       <c r="U6" s="0" t="n">
@@ -1677,16 +1677,16 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1000</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>2</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="Q7" s="0" t="n">
         <v>3</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="S7" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 45; cumulative 45; continuous theoretical DPS=14</t>
+          <t>Incremental cost 35; cumulative 35; continuous theoretical DPS=16</t>
         </is>
       </c>
       <c r="U7" s="0" t="n">
@@ -1743,13 +1743,13 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>60</v>
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
       <c r="P8" s="0" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Q8" s="0" t="n">
         <v>3</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="S8" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 60; cumulative 105; continuous theoretical DPS=31.1111</t>
+          <t>Incremental cost 60; cumulative 95; continuous theoretical DPS=24</t>
         </is>
       </c>
       <c r="U8" s="0" t="n">
@@ -1809,16 +1809,16 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>2</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q9" s="0" t="n">
         <v>3</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="S9" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 100; cumulative 205; continuous theoretical DPS=56.25</t>
+          <t>Incremental cost 95; cumulative 190; continuous theoretical DPS=32</t>
         </is>
       </c>
       <c r="U9" s="0" t="n">
@@ -1875,16 +1875,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -1902,17 +1902,17 @@
         <v>8</v>
       </c>
       <c r="P10" s="0" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="R10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="S10" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 35; cumulative 35; slow aura; DPS=0</t>
+          <t>Incremental cost 25; cumulative 25; slow aura; DPS=0</t>
         </is>
       </c>
       <c r="U10" s="0" t="n">
@@ -1941,16 +1941,16 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1968,17 +1968,17 @@
         <v>9</v>
       </c>
       <c r="P11" s="0" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="Q11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="R11" s="0" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 50; cumulative 85; slow aura; DPS=0</t>
+          <t>Incremental cost 40; cumulative 65; slow aura; DPS=0</t>
         </is>
       </c>
       <c r="U11" s="0" t="n">
@@ -2006,16 +2006,16 @@
         <v>3</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>0</v>
@@ -2033,17 +2033,17 @@
         <v>0</v>
       </c>
       <c r="P12" s="0" t="n">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="Q12" s="0" t="n">
         <v>1</v>
       </c>
       <c r="R12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 80; cumulative 165; slow aura; DPS=0</t>
+          <t>Incremental cost 65; cumulative 130; slow aura; DPS=0</t>
         </is>
       </c>
       <c r="U12" s="0" t="n">

--- a/Luban/Config/Datas/TowerInfo.xlsx
+++ b/Luban/Config/Datas/TowerInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">int </t>
+          <t>float</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -1490,7 +1490,7 @@
         <v>450</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>2</v>
       </c>
       <c r="P4" s="0" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="0" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="S4" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 25; cumulative 25; continuous theoretical DPS=13.3333</t>
+          <t>Incremental cost 32; cumulative 32; continuous theoretical DPS=13.3333</t>
         </is>
       </c>
       <c r="U4" s="0" t="n">
@@ -1546,16 +1546,16 @@
         <v>2</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1573,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="P5" s="0" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="Q5" s="0" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="S5" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 45; cumulative 70; continuous theoretical DPS=22.2222</t>
+          <t>Incremental cost 90; cumulative 122; continuous theoretical DPS=20.9302</t>
         </is>
       </c>
       <c r="U5" s="0" t="n">
@@ -1611,16 +1611,16 @@
         <v>3</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="Q6" s="0" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="S6" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 75; cumulative 145; continuous theoretical DPS=31.1111</t>
+          <t>Incremental cost 180; cumulative 302; continuous theoretical DPS=31.7073</t>
         </is>
       </c>
       <c r="U6" s="0" t="n">
@@ -1686,7 +1686,7 @@
         <v>1000</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>2</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="0" t="n">
         <v>3</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="S7" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 35; cumulative 35; continuous theoretical DPS=16</t>
+          <t>Incremental cost 44; cumulative 44; continuous theoretical DPS=16</t>
         </is>
       </c>
       <c r="U7" s="0" t="n">
@@ -1743,19 +1743,19 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
       <c r="P8" s="0" t="n">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="Q8" s="0" t="n">
         <v>3</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="S8" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 60; cumulative 95; continuous theoretical DPS=24</t>
+          <t>Incremental cost 110; cumulative 154; continuous theoretical DPS=25.2632</t>
         </is>
       </c>
       <c r="U8" s="0" t="n">
@@ -1809,19 +1809,19 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="Q9" s="0" t="n">
         <v>3</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="S9" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 95; cumulative 190; continuous theoretical DPS=32</t>
+          <t>Incremental cost 210; cumulative 364; continuous theoretical DPS=36.6667</t>
         </is>
       </c>
       <c r="U9" s="0" t="n">
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
@@ -1884,7 +1884,7 @@
         <v>250</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>8</v>
       </c>
       <c r="P10" s="0" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="0" t="n">
         <v>1</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="S10" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 25; cumulative 25; slow aura; DPS=0</t>
+          <t>Incremental cost 30; cumulative 30; slow aura; DPS=0</t>
         </is>
       </c>
       <c r="U10" s="0" t="n">
@@ -1941,16 +1941,16 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>9</v>
       </c>
       <c r="P11" s="0" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="0" t="n">
         <v>1</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 40; cumulative 65; slow aura; DPS=0</t>
+          <t>Incremental cost 85; cumulative 115; slow aura; DPS=0</t>
         </is>
       </c>
       <c r="U11" s="0" t="n">
@@ -2006,16 +2006,16 @@
         <v>3</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="0" t="n">
-        <v>91</v>
+        <v>199</v>
       </c>
       <c r="Q12" s="0" t="n">
         <v>1</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>Incremental cost 65; cumulative 130; slow aura; DPS=0</t>
+          <t>Incremental cost 170; cumulative 285; slow aura; DPS=0</t>
         </is>
       </c>
       <c r="U12" s="0" t="n">
